--- a/output/pdf_financials_xlsx/RSC.P.xlsx
+++ b/output/pdf_financials_xlsx/RSC.P.xlsx
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.07892100000000001</v>
+        <v>-0.07892100000000001</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.07892100000000001</v>
+        <v>-0.07892100000000001</v>
       </c>
     </row>
     <row r="21">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.07892100000000001</v>
+        <v>-0.07892100000000001</v>
       </c>
     </row>
     <row r="24">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.07892100000000001</v>
+        <v>-0.07892100000000001</v>
       </c>
     </row>
     <row r="28">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.07892100000000001</v>
+        <v>-0.07892100000000001</v>
       </c>
     </row>
     <row r="30">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.07892100000000001</v>
+        <v>-0.07892100000000001</v>
       </c>
     </row>
     <row r="29">

--- a/output/pdf_financials_xlsx/RSC.P.xlsx
+++ b/output/pdf_financials_xlsx/RSC.P.xlsx
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.317047</v>
       </c>
     </row>
     <row r="35">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.317047</v>
       </c>
     </row>
     <row r="37">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/RSC.P.xlsx
+++ b/output/pdf_financials_xlsx/RSC.P.xlsx
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.032128</v>
       </c>
     </row>
     <row r="108">
@@ -2656,7 +2656,11 @@
           <t>Share-based payment expense 5 (b)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
